--- a/artfynd/A 13699-2026 artfynd.xlsx
+++ b/artfynd/A 13699-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111813872</v>
+        <v>111927812</v>
       </c>
       <c r="B2" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540558</v>
+        <v>540626</v>
       </c>
       <c r="R2" t="n">
-        <v>7247553</v>
+        <v>7247582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,32 +743,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111814119</v>
+        <v>111825340</v>
       </c>
       <c r="B3" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,24 +807,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540683</v>
+        <v>540641</v>
       </c>
       <c r="R3" t="n">
-        <v>7247576</v>
+        <v>7247565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,22 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 25 rosentickor på denna låga. Ullticka, ulltickeporing, rynkskinn på samma låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,41 +906,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111814047</v>
+        <v>111928119</v>
       </c>
       <c r="B4" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -954,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540634</v>
+        <v>540609</v>
       </c>
       <c r="R4" t="n">
-        <v>7247517</v>
+        <v>7247475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,27 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>På granlåga full med ullticka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111813745</v>
+        <v>119506832</v>
       </c>
       <c r="B5" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,42 +1031,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Matsdal, granskog, Ås lm</t>
+          <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540569</v>
+        <v>540649</v>
       </c>
       <c r="R5" t="n">
-        <v>7247602</v>
+        <v>7247522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,22 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,9 +1116,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlåga, kapad över stigen</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, kapad över stigen</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,37 +1141,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111814303</v>
+        <v>111813785</v>
       </c>
       <c r="B6" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540601</v>
+        <v>540571</v>
       </c>
       <c r="R6" t="n">
-        <v>7247517</v>
+        <v>7247578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,15 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111814152</v>
+        <v>111814212</v>
       </c>
       <c r="B7" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1263,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1326,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540661</v>
+        <v>540636</v>
       </c>
       <c r="R7" t="n">
-        <v>7247564</v>
+        <v>7247596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,37 +1363,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111814064</v>
+        <v>111825158</v>
       </c>
       <c r="B8" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540672</v>
+        <v>540641</v>
       </c>
       <c r="R8" t="n">
-        <v>7247583</v>
+        <v>7247565</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,22 +1431,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,6 +1453,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1515,15 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111813722</v>
+        <v>111928110</v>
       </c>
       <c r="B9" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,31 +1495,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1563,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540583</v>
+        <v>540609</v>
       </c>
       <c r="R9" t="n">
-        <v>7247618</v>
+        <v>7247475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,22 +1552,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt, hela lågan full med ullticka. Även rosenticka på denna låga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,6 +1571,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1635,15 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111813938</v>
+        <v>111928321</v>
       </c>
       <c r="B10" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1678,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540655</v>
+        <v>540589</v>
       </c>
       <c r="R10" t="n">
-        <v>7247498</v>
+        <v>7247721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,22 +1658,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,37 +1696,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111814135</v>
+        <v>111928864</v>
       </c>
       <c r="B11" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1794,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540661</v>
+        <v>540588</v>
       </c>
       <c r="R11" t="n">
-        <v>7247564</v>
+        <v>7247583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,22 +1764,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,15 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111814212</v>
+        <v>111825098</v>
       </c>
       <c r="B12" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,21 +1808,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540636</v>
+        <v>540641</v>
       </c>
       <c r="R12" t="n">
-        <v>7247596</v>
+        <v>7247565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,22 +1865,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färskt. På granlåga med minst 25 rosentickor, ullticka och ulltickeporing.  Någon gul slemsvamp? på rynkskinnet</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,6 +1887,21 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1983,37 +1918,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111813785</v>
+        <v>111825245</v>
       </c>
       <c r="B13" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2026,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540571</v>
+        <v>540641</v>
       </c>
       <c r="R13" t="n">
-        <v>7247578</v>
+        <v>7247565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,22 +1986,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färskt exemplar. Kollekt tog och torkades, gulnade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,6 +2008,21 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2099,37 +2039,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111813975</v>
+        <v>117574986</v>
       </c>
       <c r="B14" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2142,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540644</v>
+        <v>540588</v>
       </c>
       <c r="R14" t="n">
-        <v>7247517</v>
+        <v>7247583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2172,22 +2107,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,37 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111814264</v>
+        <v>111814047</v>
       </c>
       <c r="B15" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2258,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540625</v>
+        <v>540634</v>
       </c>
       <c r="R15" t="n">
-        <v>7247625</v>
+        <v>7247517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,6 +2224,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,47 +2256,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111813707</v>
+        <v>111814064</v>
       </c>
       <c r="B16" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2379,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540647</v>
+        <v>540672</v>
       </c>
       <c r="R16" t="n">
-        <v>7247579</v>
+        <v>7247583</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,23 +2348,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2466,37 +2367,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111825098</v>
+        <v>111814135</v>
       </c>
       <c r="B17" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2509,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540641</v>
+        <v>540661</v>
       </c>
       <c r="R17" t="n">
-        <v>7247565</v>
+        <v>7247564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2539,17 +2435,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färskt. På granlåga med minst 25 rosentickor, ullticka och ulltickeporing.  Någon gul slemsvamp? på rynkskinnet</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,21 +2462,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2592,44 +2478,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111825340</v>
+        <v>111814303</v>
       </c>
       <c r="B18" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2639,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540641</v>
+        <v>540601</v>
       </c>
       <c r="R18" t="n">
-        <v>7247565</v>
+        <v>7247517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2669,17 +2546,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 25 rosentickor på denna låga. Ullticka, ulltickeporing, rynkskinn på samma låga</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,37 +2589,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111825158</v>
+        <v>111909739</v>
       </c>
       <c r="B19" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2750,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540641</v>
+        <v>540734</v>
       </c>
       <c r="R19" t="n">
-        <v>7247565</v>
+        <v>7247655</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2788,11 +2665,6 @@
           <t>2023-08-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Med ulltickeporing</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2802,21 +2674,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2833,37 +2690,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111825245</v>
+        <v>111927932</v>
       </c>
       <c r="B20" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540641</v>
+        <v>540603</v>
       </c>
       <c r="R20" t="n">
-        <v>7247565</v>
+        <v>7247579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,17 +2758,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färskt exemplar. Kollekt tog och torkades, gulnade.</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,21 +2775,6 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2959,47 +2791,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111905851</v>
+        <v>111928149</v>
       </c>
       <c r="B21" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3007,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540643</v>
+        <v>540585</v>
       </c>
       <c r="R21" t="n">
-        <v>7247578</v>
+        <v>7247527</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,12 +2859,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3051,6 +2873,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3072,12 +2895,7 @@
         <v>111928372</v>
       </c>
       <c r="B22" t="n">
-        <v>89941</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,58 +2993,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111928767</v>
+        <v>119506931</v>
       </c>
       <c r="B23" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Matsdal, granskog, Ås lm</t>
+          <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540472</v>
+        <v>540594</v>
       </c>
       <c r="R23" t="n">
-        <v>7247569</v>
+        <v>7247724</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3253,12 +3058,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,6 +3079,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3285,47 +3115,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111928807</v>
+        <v>111928641</v>
       </c>
       <c r="B24" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3333,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540500</v>
+        <v>540502</v>
       </c>
       <c r="R24" t="n">
-        <v>7247569</v>
+        <v>7247613</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3371,12 +3191,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Förekommer i området</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3395,15 +3221,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111928431</v>
+        <v>111813707</v>
       </c>
       <c r="B25" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3411,26 +3232,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3438,10 +3264,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540531</v>
+        <v>540647</v>
       </c>
       <c r="R25" t="n">
-        <v>7247629</v>
+        <v>7247579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3468,12 +3294,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,9 +3318,23 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3501,15 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111927812</v>
+        <v>111813722</v>
       </c>
       <c r="B26" t="n">
-        <v>85850</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3517,26 +3362,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3544,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540626</v>
+        <v>540582</v>
       </c>
       <c r="R26" t="n">
-        <v>7247582</v>
+        <v>7247618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3574,43 +3424,32 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3627,42 +3466,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111927932</v>
+        <v>111813745</v>
       </c>
       <c r="B27" t="n">
-        <v>90235</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3670,10 +3509,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540603</v>
+        <v>540569</v>
       </c>
       <c r="R27" t="n">
-        <v>7247579</v>
+        <v>7247602</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3700,12 +3539,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3714,9 +3563,23 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3733,15 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111928321</v>
+        <v>111813872</v>
       </c>
       <c r="B28" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3749,26 +3607,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3776,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540589</v>
+        <v>540557</v>
       </c>
       <c r="R28" t="n">
-        <v>7247721</v>
+        <v>7247553</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3806,17 +3669,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,7 +3693,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3844,15 +3711,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111929133</v>
+        <v>111905851</v>
       </c>
       <c r="B29" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3860,26 +3722,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3887,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540589</v>
+        <v>540643</v>
       </c>
       <c r="R29" t="n">
-        <v>7247593</v>
+        <v>7247578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3917,12 +3784,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3931,7 +3798,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3950,15 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111928641</v>
+        <v>111928182</v>
       </c>
       <c r="B30" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,26 +3827,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3993,10 +3859,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540501</v>
+        <v>540578</v>
       </c>
       <c r="R30" t="n">
-        <v>7247613</v>
+        <v>7247609</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4031,18 +3897,12 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Förekommer i området</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4061,42 +3921,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111928149</v>
+        <v>111928307</v>
       </c>
       <c r="B31" t="n">
-        <v>90235</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4104,10 +3964,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540585</v>
+        <v>540614</v>
       </c>
       <c r="R31" t="n">
-        <v>7247527</v>
+        <v>7247718</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4148,7 +4008,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4167,15 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111928864</v>
+        <v>111928767</v>
       </c>
       <c r="B32" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4183,26 +4037,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4210,10 +4069,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540588</v>
+        <v>540472</v>
       </c>
       <c r="R32" t="n">
-        <v>7247583</v>
+        <v>7247569</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,7 +4113,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4273,15 +4131,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111928307</v>
+        <v>111928807</v>
       </c>
       <c r="B33" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4321,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540614</v>
+        <v>540500</v>
       </c>
       <c r="R33" t="n">
-        <v>7247718</v>
+        <v>7247569</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4383,15 +4236,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111928182</v>
+        <v>119506757</v>
       </c>
       <c r="B34" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4417,24 +4265,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Matsdal, granskog, Ås lm</t>
+          <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540578</v>
+        <v>540600</v>
       </c>
       <c r="R34" t="n">
-        <v>7247609</v>
+        <v>7247693</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4461,12 +4306,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, färska rikligt, högt upp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4477,6 +4327,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4493,15 +4358,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111939435</v>
+        <v>119506759</v>
       </c>
       <c r="B35" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4509,37 +4369,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Matsdal, granskog, Ås lm</t>
+          <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540686</v>
+        <v>540625</v>
       </c>
       <c r="R35" t="n">
-        <v>7247572</v>
+        <v>7247564</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4566,12 +4428,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, färska rikligt, högt upp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4580,7 +4447,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4594,14 +4460,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Gammal gran</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies # Gammal gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4619,53 +4480,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117574986</v>
+        <v>119506770</v>
       </c>
       <c r="B36" t="n">
-        <v>90843</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Matsdal, granskog, Ås lm</t>
+          <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540588</v>
+        <v>540610</v>
       </c>
       <c r="R36" t="n">
-        <v>7247583</v>
+        <v>7247727</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4692,12 +4550,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4706,9 +4569,23 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4725,15 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119506897</v>
+        <v>119506806</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4741,34 +4613,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540594</v>
+        <v>540649</v>
       </c>
       <c r="R37" t="n">
-        <v>7247725</v>
+        <v>7247516</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4812,26 +4693,6 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
@@ -4844,624 +4705,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>119506832</v>
-      </c>
-      <c r="B38" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>658</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>540649</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7247522</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Granlåga, kapad över stigen</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, kapad över stigen</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>119506759</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>540625</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7247564</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska rikligt, högt upp</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>119506931</v>
-      </c>
-      <c r="B40" t="n">
-        <v>90957</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>4217</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Blodticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Meruliopsis taxicola</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>540594</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7247724</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>119506806</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>540649</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7247516</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>119506757</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>540600</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7247693</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, färska rikligt, högt upp</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
